--- a/datasets/day1_excel_foundations/05_functions_and_data_tips/d1_m5_functions_start.xlsx
+++ b/datasets/day1_excel_foundations/05_functions_and_data_tips/d1_m5_functions_start.xlsx
@@ -613,7 +613,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>119.7</v>
+        <v>120</v>
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         <v>2</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3332</v>
+        <v>3000</v>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1454.4</v>
+        <v>1400</v>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>806</v>
+        <v>600</v>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1656</v>
+        <v>1600</v>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>3</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>326.25</v>
+        <v>300</v>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>779.2</v>
+        <v>1000</v>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>587.2</v>
+        <v>600</v>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>801.6</v>
+        <v>1200</v>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>1663</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="13">
@@ -1027,7 +1027,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>1037</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14">
@@ -1063,7 +1063,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>724</v>
+        <v>800</v>
       </c>
     </row>
     <row r="15">
@@ -1099,7 +1099,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>177</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -1135,7 +1135,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>653.8</v>
+        <v>800</v>
       </c>
     </row>
     <row r="17">
@@ -1171,7 +1171,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>1758</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="18">
@@ -1207,7 +1207,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>56.1</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>1148</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="20">
@@ -1279,7 +1279,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>905.25</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="21">
@@ -1315,7 +1315,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>918</v>
+        <v>600</v>
       </c>
     </row>
     <row r="22">
@@ -1351,7 +1351,7 @@
         <v>3</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>1806.9</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="23">
@@ -1387,7 +1387,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>672.8</v>
+        <v>700</v>
       </c>
     </row>
     <row r="24">
@@ -1423,7 +1423,7 @@
         <v>2</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>619.4</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25">
@@ -1459,7 +1459,7 @@
         <v>2</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>370</v>
+        <v>300</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>882</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="27">
@@ -1531,7 +1531,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>190.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -1567,7 +1567,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>1696</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="29">
@@ -1603,7 +1603,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>102.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -1639,7 +1639,7 @@
         <v>2</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>258.4</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31">
@@ -1675,7 +1675,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>263</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/day1_excel_foundations/05_functions_and_data_tips/d1_m5_functions_start.xlsx
+++ b/datasets/day1_excel_foundations/05_functions_and_data_tips/d1_m5_functions_start.xlsx
@@ -471,13 +471,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
     <col width="19.5" customWidth="1" min="3" max="3"/>
-    <col width="10.5" customWidth="1" min="4" max="4"/>
+    <col width="14.5" customWidth="1" min="4" max="4"/>
     <col width="22.5" customWidth="1" min="5" max="5"/>
     <col width="12.5" customWidth="1" min="6" max="6"/>
     <col width="10.5" customWidth="1" min="7" max="7"/>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
@@ -694,10 +694,10 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1400</v>
+        <v>2800</v>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
@@ -755,33 +755,33 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>45938</v>
+        <v>45694</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amara Otieno</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
@@ -797,33 +797,33 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>45458</v>
+        <v>45922</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smart Home</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
@@ -881,11 +881,11 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>45856</v>
+        <v>46084</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -895,19 +895,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>USB-C Hub 7in1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Accessory</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
@@ -923,11 +923,11 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>45383</v>
+        <v>45796</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nyasha Banda</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -937,19 +937,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HP Spectre x360</t>
+          <t>Surface Go 4</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
@@ -965,33 +965,33 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46317</v>
+        <v>46200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kudzai Sibanda</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Pixel 9 Pro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>1400</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="13">
@@ -1001,33 +1001,33 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>45857</v>
+        <v>45944</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tendai Moyo</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>Echo Dot 6</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1037,11 +1037,11 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>45994</v>
+        <v>46365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Tatenda Mpofu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1051,19 +1051,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>HP Spectre x360</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="15">
@@ -1073,33 +1073,33 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>45453</v>
+        <v>45682</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nyasha Banda</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Galaxy Tab S10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smart Home</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16">
@@ -1109,33 +1109,33 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>46287</v>
+        <v>46210</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Wireless Mouse Pro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Accessory</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
@@ -1145,33 +1145,33 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>46107</v>
+        <v>45734</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>OnePlus 13</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18">
@@ -1181,33 +1181,33 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>46011</v>
+        <v>46347</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tatenda Mpofu</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bluetooth Headphones</t>
+          <t>Google Nest Hub 3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Accessory</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19">
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>45508</v>
+        <v>45902</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1231,19 +1231,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Laptop Sleeve 15in</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Accessory</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>1400</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20">
@@ -1253,11 +1253,11 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>45671</v>
+        <v>46065</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kudzai Sibanda</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1267,16 +1267,16 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>1400</v>
@@ -1289,11 +1289,11 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>45306</v>
+        <v>45824</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rutendo Chikafu</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1303,378 +1303,18 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>O0021</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>45939</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Kudzai Sibanda</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Galaxy Tab S10</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>O0022</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>45884</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>iPad Air 6</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>O0023</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>45522</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>O0024</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>46343</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Farai Ncube</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>O0025</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>46363</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>ThinkPad X1</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>O0026</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>46017</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Tendai Moyo</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Echo Dot 6</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>O0027</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>46252</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Simbarashe Mutasa</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>MacBook Air M4</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>O0028</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>46162</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Chipo Marufu</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Laptop Sleeve 15in</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Accessory</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>O0029</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>45498</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Kudzai Sibanda</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Bluetooth Headphones</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Accessory</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>O0030</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>46183</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Simbarashe Mutasa</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Ring Doorbell Pro</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="5" t="n">
         <v>200</v>
       </c>
     </row>

--- a/datasets/day1_excel_foundations/05_functions_and_data_tips/d1_m5_functions_start.xlsx
+++ b/datasets/day1_excel_foundations/05_functions_and_data_tips/d1_m5_functions_start.xlsx
@@ -1372,35 +1372,35 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>L2:  =SUM(H2:H31)          adds everything up</t>
+          <t>L2:  =SUM(H2:H21)          adds everything up</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>L3:  =AVERAGE(H2:H31)      the mean</t>
+          <t>L3:  =AVERAGE(H2:H21)      the mean</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>L4:  =MAX(H2:H31)          the biggest value</t>
+          <t>L4:  =MAX(H2:H21)          the biggest value</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>L5:  =MIN(H2:H31)          the smallest value</t>
+          <t>L5:  =MIN(H2:H21)          the smallest value</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>L6:  =COUNT(H2:H31)        how many numbers are in the range</t>
+          <t>L6:  =COUNT(H2:H21)        how many numbers are in the range</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Tip: instead of typing H2:H31, type =SUM( then drag over the cells with your mouse.</t>
+          <t>Tip: instead of typing H2:H21, type =SUM( then drag over the cells with your mouse.</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>STEP 2 - Total units. L7:  =SUM(G2:G31)</t>
+          <t>STEP 2 - Total units. L7:  =SUM(G2:G21)</t>
         </is>
       </c>
     </row>
@@ -1437,21 +1437,21 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>L8:  =COUNTIF(F2:F31,"Laptop")             how many orders were laptops</t>
+          <t>L8:  =COUNTIF(F2:F21,"Laptop")             how many orders were laptops</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>L9:  =SUMIF(F2:F31,"Laptop",H2:H31)        how much money laptops brought in</t>
+          <t>L9:  =SUMIF(F2:F21,"Laptop",H2:H21)        how much money laptops brought in</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Read SUMIF as: look in F2:F31, wherever you find 'Laptop', add up the matching H value.</t>
+          <t>Read SUMIF as: look in F2:F21, wherever you find 'Laptop', add up the matching H value.</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>otherwise say Small. Copy it down to I31.</t>
+          <t>otherwise say Small. Copy it down to I21.</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>STEP 5 - Now count your own results.  L10:  =COUNTIF(I2:I31,"Large")</t>
+          <t>STEP 5 - Now count your own results.  L10:  =COUNTIF(I2:I21,"Large")</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>STEP 6 - One more condition.  L11:  =SUMIF(D2:D31,"Zimbabwe",H2:H31)</t>
+          <t>STEP 6 - One more condition.  L11:  =SUMIF(D2:D21,"Zimbabwe",H2:H21)</t>
         </is>
       </c>
     </row>
